--- a/tables/tables_summary.xlsx
+++ b/tables/tables_summary.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -582,7 +582,11 @@
           <t>1 (16.7%)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -610,7 +614,11 @@
           <t>1 (16.7%)</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -638,7 +646,11 @@
           <t>2 (33.3%)</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -710,7 +722,11 @@
           <t>0 (0.0%)</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -738,7 +754,11 @@
           <t>0 (0.0%)</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -766,7 +786,11 @@
           <t>0 (0.0%)</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -794,7 +818,11 @@
           <t>4 (66.7%)</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr"/>
@@ -925,29 +953,49 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Average self-assessment (0–10)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>4.2 (1.8–6.3)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>6.0 (2.3–7.0)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>3.0 (3.0–8.3)</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>3.3 (1.8–5.8)</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>0.761</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Panel C — Knowledge Assessment Outcomes</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Knowledge outcomes, median (IQR)</t>
+          <t>Panel C — Knowledge Assessment Outcomes</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
@@ -957,61 +1005,41 @@
       <c r="F22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Total correct (out of 12)</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>8.0 (7.0–9.8)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>8.0 (6.5–8.5)</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>9.0 (7.0–10.0)</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>8.5 (7.2–10.5)</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>0.577</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Knowledge outcomes, median (IQR)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total incorrect</t>
+          <t xml:space="preserve">  Total correct (out of 12)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>4.0 (2.2–5.0)</t>
+          <t>8.0 (7.0–9.8)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>4.0 (3.5–5.5)</t>
+          <t>8.0 (6.5–8.5)</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3.0 (2.0–5.0)</t>
+          <t>9.0 (7.0–10.0)</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>3.5 (1.5–4.8)</t>
+          <t>8.5 (7.2–10.5)</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1023,91 +1051,111 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total ‘not sure’</t>
+          <t xml:space="preserve">  Total incorrect</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>0.0 (0.0–0.0)</t>
+          <t>4.0 (2.2–5.0)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>0.0 (0.0–1.5)</t>
+          <t>4.0 (3.5–5.5)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>0.0 (0.0–0.0)</t>
+          <t>3.0 (2.0–5.0)</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>0.0 (0.0–0.0)</t>
+          <t>3.5 (1.5–4.8)</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>0.577</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Total ‘not sure’</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>0.0 (0.0–0.0)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>0.0 (0.0–1.5)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>0.0 (0.0–0.0)</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>0.0 (0.0–0.0)</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>0.405</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Percent correct of attempted (%)</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>66.7 (58.3–81.2)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>66.7 (54.2–70.8)</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>75.0 (58.3–83.3)</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>70.8 (60.4–87.5)</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>0.577</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr"/>
-      <c r="B27" s="3" t="inlineStr"/>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
-    </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Panel D — Survey Duration</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr"/>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Survey duration, median (IQR)</t>
+          <t>Panel D — Survey Duration</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
@@ -1117,47 +1165,59 @@
       <c r="F29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Survey duration, median (IQR)</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Completion time (min)</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>8.3 (6.0–14.7)</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>5.9 (5.1–7.0)</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>14.8 (10.4–17.8)</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>10.2 (7.0–13.7)</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>0.145</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-    </row>
-    <row r="32" ht="80" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="80" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Participants (N = 18) were randomly assigned to one of three resource groups: No Resource (n = 7), PDF reference (n = 5), or ChatGPT (n = 6). Continuous and ordinal variables are reported as median (Q1–Q3); categorical variables as n (%). Between-group differences for ordinal and continuous variables were assessed with the Kruskal-Wallis rank-sum test, a non-parametric method selected a priori given the small, unequal group sizes (n = 5–7), for which parametric assumptions cannot be reliably verified. Categorical demographic variables (education level, specialty) were not tested for between-group differences (NT) because the sparse contingency tables (N = 18 across 3 groups) produced expected cell counts &lt; 5 in the majority of cells, violating the assumptions of both the chi-square test and Fisher’s exact test. IQR, interquartile range; NT, not tested.</t>
         </is>
@@ -1165,7 +1225,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:F33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tables/tables_summary.xlsx
+++ b/tables/tables_summary.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Table 1 — Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 — Per-question" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Table 3 — Correlation" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,12 +1057,12 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>4.0 (2.2–5.0)</t>
+          <t>3.5 (2.2–4.0)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>4.0 (3.5–5.5)</t>
+          <t>4.0 (3.0–4.0)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1071,12 +1072,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>3.5 (1.5–4.8)</t>
+          <t>3.5 (1.5–4.0)</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>0.890</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1121,12 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>66.7 (58.3–81.2)</t>
+          <t>66.7 (62.8–81.2)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>66.7 (54.2–70.8)</t>
+          <t>66.7 (64.6–70.8)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1135,12 +1136,12 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>70.8 (60.4–87.5)</t>
+          <t>70.8 (64.4–87.5)</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>0.726</t>
         </is>
       </c>
     </row>
@@ -1752,4 +1753,145 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>rho</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p_bonferroni</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>All Participants</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.595</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>No Resource</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.011</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Spearman rank-order correlation between average self-rated confidence (self_confidence_mean, 0–10 scale) and total correct responses (n_correct, 0–12) for the full sample and each experimental group. Bonferroni-adjusted p-values account for 4 simultaneous tests (adjusted α = 0.0125). Per-group estimates are based on very small subsamples (n = 5–7) and should be interpreted with caution.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:E7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>